--- a/docs/idea/problem4/step2/D2_D3高置信_风险IPC排查.xlsx
+++ b/docs/idea/problem4/step2/D2_D3高置信_风险IPC排查.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S296"/>
+  <dimension ref="A1:T296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -524,6 +524,11 @@
           <t>last_label</t>
         </is>
       </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>是否毫不相关</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -622,6 +627,11 @@
           <t>无源手术器械</t>
         </is>
       </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -720,6 +730,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -818,6 +833,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -916,6 +936,11 @@
           <t>医用软件</t>
         </is>
       </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1014,6 +1039,11 @@
           <t>医用康复器械</t>
         </is>
       </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1112,6 +1142,11 @@
           <t>医用成像器械</t>
         </is>
       </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1210,6 +1245,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1307,6 +1347,11 @@
           <t>医用软件</t>
         </is>
       </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1405,6 +1450,11 @@
           <t>无源手术器械</t>
         </is>
       </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1503,6 +1553,11 @@
           <t>无源手术器械</t>
         </is>
       </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1601,6 +1656,11 @@
           <t>无源手术器械</t>
         </is>
       </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1699,6 +1759,11 @@
           <t>无源手术器械</t>
         </is>
       </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1797,6 +1862,11 @@
           <t>无源手术器械</t>
         </is>
       </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1895,6 +1965,11 @@
           <t>无源手术器械</t>
         </is>
       </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1993,6 +2068,11 @@
           <t>无源手术器械</t>
         </is>
       </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2091,6 +2171,11 @@
           <t>无源手术器械</t>
         </is>
       </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2189,6 +2274,11 @@
           <t>无源手术器械</t>
         </is>
       </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2287,6 +2377,11 @@
           <t>无源手术器械</t>
         </is>
       </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2385,6 +2480,11 @@
           <t>无源手术器械</t>
         </is>
       </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2483,6 +2583,11 @@
           <t>无源手术器械</t>
         </is>
       </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2581,6 +2686,11 @@
           <t>无源手术器械</t>
         </is>
       </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2679,6 +2789,11 @@
           <t>无源手术器械</t>
         </is>
       </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2777,6 +2892,11 @@
           <t>无源手术器械</t>
         </is>
       </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2875,6 +2995,11 @@
           <t>无源手术器械</t>
         </is>
       </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2973,6 +3098,11 @@
           <t>无源手术器械</t>
         </is>
       </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3071,6 +3201,11 @@
           <t>神经和心血管手术器械</t>
         </is>
       </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3169,6 +3304,11 @@
           <t>骨科手术器械</t>
         </is>
       </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3267,6 +3407,11 @@
           <t>骨科手术器械</t>
         </is>
       </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3365,6 +3510,11 @@
           <t>骨科手术器械</t>
         </is>
       </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3463,6 +3613,11 @@
           <t>骨科手术器械</t>
         </is>
       </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3561,6 +3716,11 @@
           <t>骨科手术器械</t>
         </is>
       </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3659,6 +3819,11 @@
           <t>骨科手术器械</t>
         </is>
       </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3757,6 +3922,11 @@
           <t>骨科手术器械</t>
         </is>
       </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3855,6 +4025,11 @@
           <t>骨科手术器械</t>
         </is>
       </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3953,6 +4128,11 @@
           <t>骨科手术器械</t>
         </is>
       </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4051,6 +4231,11 @@
           <t>骨科手术器械</t>
         </is>
       </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4149,6 +4334,11 @@
           <t>骨科手术器械</t>
         </is>
       </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4247,6 +4437,11 @@
           <t>骨科手术器械</t>
         </is>
       </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4345,6 +4540,11 @@
           <t>骨科手术器械</t>
         </is>
       </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4443,6 +4643,11 @@
           <t>骨科手术器械</t>
         </is>
       </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4541,6 +4746,11 @@
           <t>骨科手术器械</t>
         </is>
       </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4639,6 +4849,11 @@
           <t>骨科手术器械</t>
         </is>
       </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4737,6 +4952,11 @@
           <t>骨科手术器械</t>
         </is>
       </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4835,6 +5055,11 @@
           <t>骨科手术器械</t>
         </is>
       </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4933,6 +5158,11 @@
           <t>骨科手术器械</t>
         </is>
       </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5031,6 +5261,11 @@
           <t>骨科手术器械</t>
         </is>
       </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5129,6 +5364,11 @@
           <t>骨科手术器械</t>
         </is>
       </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5227,6 +5467,11 @@
           <t>骨科手术器械</t>
         </is>
       </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5325,6 +5570,11 @@
           <t>骨科手术器械</t>
         </is>
       </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5423,6 +5673,11 @@
           <t>骨科手术器械</t>
         </is>
       </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5521,6 +5776,11 @@
           <t>骨科手术器械</t>
         </is>
       </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5619,6 +5879,11 @@
           <t>骨科手术器械</t>
         </is>
       </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5717,6 +5982,11 @@
           <t>骨科手术器械</t>
         </is>
       </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5815,6 +6085,11 @@
           <t>医用成像器械</t>
         </is>
       </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5913,6 +6188,11 @@
           <t>医用成像器械</t>
         </is>
       </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -6011,6 +6291,11 @@
           <t>医用成像器械</t>
         </is>
       </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -6109,6 +6394,11 @@
           <t>医用成像器械</t>
         </is>
       </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6207,6 +6497,11 @@
           <t>医用成像器械</t>
         </is>
       </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -6305,6 +6600,11 @@
           <t>医用成像器械</t>
         </is>
       </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -6403,6 +6703,11 @@
           <t>医用成像器械</t>
         </is>
       </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -6501,6 +6806,11 @@
           <t>医用成像器械</t>
         </is>
       </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6598,6 +6908,11 @@
           <t>医用成像器械</t>
         </is>
       </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6696,6 +7011,11 @@
           <t>医用成像器械</t>
         </is>
       </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -6794,6 +7114,11 @@
           <t>医用成像器械</t>
         </is>
       </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -6892,6 +7217,11 @@
           <t>医用成像器械</t>
         </is>
       </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -6990,6 +7320,11 @@
           <t>医用成像器械</t>
         </is>
       </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -7088,6 +7423,11 @@
           <t>医用成像器械</t>
         </is>
       </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -7186,6 +7526,11 @@
           <t>医用成像器械</t>
         </is>
       </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -7284,6 +7629,11 @@
           <t>医用成像器械</t>
         </is>
       </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -7382,6 +7732,11 @@
           <t>医用成像器械</t>
         </is>
       </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -7480,6 +7835,11 @@
           <t>医用成像器械</t>
         </is>
       </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -7578,6 +7938,11 @@
           <t>医用成像器械</t>
         </is>
       </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -7676,6 +8041,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -7774,6 +8144,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -7872,6 +8247,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -7970,6 +8350,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -8068,6 +8453,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -8166,6 +8556,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -8264,6 +8659,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -8362,6 +8762,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -8460,6 +8865,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -8558,6 +8968,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -8656,6 +9071,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -8754,6 +9174,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -8852,6 +9277,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -8950,6 +9380,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -9048,6 +9483,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -9146,6 +9586,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -9244,6 +9689,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -9342,6 +9792,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -9440,6 +9895,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -9538,6 +9998,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -9636,6 +10101,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -9734,6 +10204,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -9832,6 +10307,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -9930,6 +10410,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -10028,6 +10513,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -10126,6 +10616,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -10224,6 +10719,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -10322,6 +10822,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -10420,6 +10925,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -10518,6 +11028,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -10616,6 +11131,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -10714,6 +11234,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -10812,6 +11337,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -10910,6 +11440,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -11008,6 +11543,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -11106,6 +11646,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -11204,6 +11749,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -11302,6 +11852,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -11400,6 +11955,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -11498,6 +12058,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -11596,6 +12161,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -11694,6 +12264,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -11792,6 +12367,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -11890,6 +12470,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -11988,6 +12573,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -12086,6 +12676,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -12184,6 +12779,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -12282,6 +12882,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -12380,6 +12985,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -12478,6 +13088,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -12576,6 +13191,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -12674,6 +13294,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -12772,6 +13397,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -12870,6 +13500,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -12968,6 +13603,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -13066,6 +13706,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -13164,6 +13809,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -13262,6 +13912,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -13360,6 +14015,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -13458,6 +14118,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -13556,6 +14221,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -13654,6 +14324,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -13752,6 +14427,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -13850,6 +14530,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -13948,6 +14633,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -14046,6 +14736,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -14144,6 +14839,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -14242,6 +14942,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -14340,6 +15045,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -14438,6 +15148,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -14536,6 +15251,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -14634,6 +15354,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -14732,6 +15457,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -14830,6 +15560,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -14928,6 +15663,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -15026,6 +15766,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -15124,6 +15869,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -15222,6 +15972,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -15320,6 +16075,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -15418,6 +16178,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -15516,6 +16281,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -15614,6 +16384,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -15712,6 +16487,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -15810,6 +16590,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -15908,6 +16693,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -16006,6 +16796,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -16104,6 +16899,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -16202,6 +17002,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -16300,6 +17105,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -16398,6 +17208,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -16496,6 +17311,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -16594,6 +17414,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -16692,6 +17517,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -16790,6 +17620,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -16888,6 +17723,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -16986,6 +17826,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -17084,6 +17929,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -17182,6 +18032,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -17280,6 +18135,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -17378,6 +18238,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -17476,6 +18341,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -17574,6 +18444,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -17672,6 +18547,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T176" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -17770,6 +18650,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -17868,6 +18753,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -17966,6 +18856,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -18064,6 +18959,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T180" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -18162,6 +19062,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T181" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -18260,6 +19165,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T182" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -18358,6 +19268,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -18456,6 +19371,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -18554,6 +19474,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -18652,6 +19577,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -18750,6 +19680,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -18848,6 +19783,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T188" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -18946,6 +19886,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T189" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -19044,6 +19989,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -19142,6 +20092,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T191" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -19240,6 +20195,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T192" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -19338,6 +20298,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T193" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -19436,6 +20401,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T194" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -19534,6 +20504,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T195" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -19632,6 +20607,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T196" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -19730,6 +20710,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T197" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -19828,6 +20813,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T198" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -19926,6 +20916,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -20024,6 +21019,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -20122,6 +21122,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -20220,6 +21225,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T202" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -20318,6 +21328,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T203" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -20416,6 +21431,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -20514,6 +21534,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T205" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -20612,6 +21637,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -20710,6 +21740,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T207" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -20808,6 +21843,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T208" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -20906,6 +21946,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T209" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -21004,6 +22049,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T210" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -21102,6 +22152,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T211" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -21200,6 +22255,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T212" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -21298,6 +22358,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T213" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -21396,6 +22461,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T214" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -21494,6 +22564,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T215" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -21592,6 +22667,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T216" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -21690,6 +22770,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T217" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -21788,6 +22873,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T218" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -21886,6 +22976,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T219" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -21984,6 +23079,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T220" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -22082,6 +23182,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T221" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -22180,6 +23285,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T222" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -22278,6 +23388,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T223" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -22376,6 +23491,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T224" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -22474,6 +23594,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T225" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -22572,6 +23697,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T226" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -22670,6 +23800,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T227" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -22768,6 +23903,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T228" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -22866,6 +24006,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T229" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -22964,6 +24109,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T230" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -23062,6 +24212,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T231" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -23160,6 +24315,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T232" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -23258,6 +24418,11 @@
           <t>医用诊察和监护器械</t>
         </is>
       </c>
+      <c r="T233" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -23356,6 +24521,11 @@
           <t>呼吸、麻醉和急救器械</t>
         </is>
       </c>
+      <c r="T234" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -23454,6 +24624,11 @@
           <t>呼吸、麻醉和急救器械</t>
         </is>
       </c>
+      <c r="T235" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -23552,6 +24727,11 @@
           <t>呼吸、麻醉和急救器械</t>
         </is>
       </c>
+      <c r="T236" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -23650,6 +24830,11 @@
           <t>物理治疗器械</t>
         </is>
       </c>
+      <c r="T237" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -23748,6 +24933,11 @@
           <t>物理治疗器械</t>
         </is>
       </c>
+      <c r="T238" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -23846,6 +25036,11 @@
           <t>医疗器械消毒灭菌器械</t>
         </is>
       </c>
+      <c r="T239" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -23944,6 +25139,11 @@
           <t>有源植入器械</t>
         </is>
       </c>
+      <c r="T240" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -24042,6 +25242,11 @@
           <t>有源植入器械</t>
         </is>
       </c>
+      <c r="T241" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -24140,6 +25345,11 @@
           <t>有源植入器械</t>
         </is>
       </c>
+      <c r="T242" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -24238,6 +25448,11 @@
           <t>注输、护理和防护器械</t>
         </is>
       </c>
+      <c r="T243" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -24336,6 +25551,11 @@
           <t>注输、护理和防护器械</t>
         </is>
       </c>
+      <c r="T244" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -24432,6 +25652,11 @@
           <t>注输、护理和防护器械</t>
         </is>
       </c>
+      <c r="T245" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -24528,6 +25753,11 @@
           <t>注输、护理和防护器械</t>
         </is>
       </c>
+      <c r="T246" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -24626,6 +25856,11 @@
           <t>注输、护理和防护器械</t>
         </is>
       </c>
+      <c r="T247" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -24724,6 +25959,11 @@
           <t>患者承载器械</t>
         </is>
       </c>
+      <c r="T248" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -24822,6 +26062,11 @@
           <t>眼科器械</t>
         </is>
       </c>
+      <c r="T249" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -24920,6 +26165,11 @@
           <t>眼科器械</t>
         </is>
       </c>
+      <c r="T250" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -25018,6 +26268,11 @@
           <t>眼科器械</t>
         </is>
       </c>
+      <c r="T251" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -25116,6 +26371,11 @@
           <t>眼科器械</t>
         </is>
       </c>
+      <c r="T252" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -25214,6 +26474,11 @@
           <t>眼科器械</t>
         </is>
       </c>
+      <c r="T253" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -25312,6 +26577,11 @@
           <t>眼科器械</t>
         </is>
       </c>
+      <c r="T254" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -25410,6 +26680,11 @@
           <t>眼科器械</t>
         </is>
       </c>
+      <c r="T255" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -25508,6 +26783,11 @@
           <t>眼科器械</t>
         </is>
       </c>
+      <c r="T256" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -25606,6 +26886,11 @@
           <t>眼科器械</t>
         </is>
       </c>
+      <c r="T257" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -25704,6 +26989,11 @@
           <t>口腔科器械</t>
         </is>
       </c>
+      <c r="T258" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -25802,6 +27092,11 @@
           <t>口腔科器械</t>
         </is>
       </c>
+      <c r="T259" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -25900,6 +27195,11 @@
           <t>口腔科器械</t>
         </is>
       </c>
+      <c r="T260" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -25998,6 +27298,11 @@
           <t>口腔科器械</t>
         </is>
       </c>
+      <c r="T261" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -26096,6 +27401,11 @@
           <t>口腔科器械</t>
         </is>
       </c>
+      <c r="T262" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -26194,6 +27504,11 @@
           <t>妇产科、辅助生殖和避孕器械</t>
         </is>
       </c>
+      <c r="T263" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -26292,6 +27607,11 @@
           <t>妇产科、辅助生殖和避孕器械</t>
         </is>
       </c>
+      <c r="T264" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -26390,6 +27710,11 @@
           <t>妇产科、辅助生殖和避孕器械</t>
         </is>
       </c>
+      <c r="T265" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -26488,6 +27813,11 @@
           <t>妇产科、辅助生殖和避孕器械</t>
         </is>
       </c>
+      <c r="T266" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -26586,6 +27916,11 @@
           <t>医用康复器械</t>
         </is>
       </c>
+      <c r="T267" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -26684,6 +28019,11 @@
           <t>医用康复器械</t>
         </is>
       </c>
+      <c r="T268" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -26782,6 +28122,11 @@
           <t>医用康复器械</t>
         </is>
       </c>
+      <c r="T269" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -26880,6 +28225,11 @@
           <t>医用康复器械</t>
         </is>
       </c>
+      <c r="T270" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -26978,6 +28328,11 @@
           <t>医用康复器械</t>
         </is>
       </c>
+      <c r="T271" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -27076,6 +28431,11 @@
           <t>医用康复器械</t>
         </is>
       </c>
+      <c r="T272" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -27174,6 +28534,11 @@
           <t>医用康复器械</t>
         </is>
       </c>
+      <c r="T273" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -27271,6 +28636,11 @@
           <t>中医器械</t>
         </is>
       </c>
+      <c r="T274" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -27369,6 +28739,11 @@
           <t>医用软件</t>
         </is>
       </c>
+      <c r="T275" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -27467,6 +28842,11 @@
           <t>医用软件</t>
         </is>
       </c>
+      <c r="T276" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -27565,6 +28945,11 @@
           <t>医用软件</t>
         </is>
       </c>
+      <c r="T277" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -27663,6 +29048,11 @@
           <t>医用软件</t>
         </is>
       </c>
+      <c r="T278" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -27761,6 +29151,11 @@
           <t>医用软件</t>
         </is>
       </c>
+      <c r="T279" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -27859,6 +29254,11 @@
           <t>医用软件</t>
         </is>
       </c>
+      <c r="T280" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -27957,6 +29357,11 @@
           <t>医用软件</t>
         </is>
       </c>
+      <c r="T281" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -28055,6 +29460,11 @@
           <t>医用软件</t>
         </is>
       </c>
+      <c r="T282" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -28153,6 +29563,11 @@
           <t>医用软件</t>
         </is>
       </c>
+      <c r="T283" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -28251,6 +29666,11 @@
           <t>医用软件</t>
         </is>
       </c>
+      <c r="T284" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -28349,6 +29769,11 @@
           <t>医用软件</t>
         </is>
       </c>
+      <c r="T285" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -28447,6 +29872,11 @@
           <t>医用软件</t>
         </is>
       </c>
+      <c r="T286" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -28545,6 +29975,11 @@
           <t>医用软件</t>
         </is>
       </c>
+      <c r="T287" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -28643,6 +30078,11 @@
           <t>医用软件</t>
         </is>
       </c>
+      <c r="T288" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -28741,6 +30181,11 @@
           <t>医用软件</t>
         </is>
       </c>
+      <c r="T289" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -28839,6 +30284,11 @@
           <t>医用软件</t>
         </is>
       </c>
+      <c r="T290" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -28937,6 +30387,11 @@
           <t>医用软件</t>
         </is>
       </c>
+      <c r="T291" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -29035,6 +30490,11 @@
           <t>医用软件</t>
         </is>
       </c>
+      <c r="T292" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -29133,6 +30593,11 @@
           <t>医用软件</t>
         </is>
       </c>
+      <c r="T293" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -29231,6 +30696,11 @@
           <t>临床检验器械</t>
         </is>
       </c>
+      <c r="T294" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -29329,6 +30799,11 @@
           <t>临床检验器械</t>
         </is>
       </c>
+      <c r="T295" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -29425,6 +30900,11 @@
       <c r="S296" t="inlineStr">
         <is>
           <t>临床检验器械</t>
+        </is>
+      </c>
+      <c r="T296" t="inlineStr">
+        <is>
+          <t>是</t>
         </is>
       </c>
     </row>
